--- a/artfynd/A 55649-2024 artfynd.xlsx
+++ b/artfynd/A 55649-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94011931</v>
+        <v>94011832</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698597.7343068155</v>
+        <v>698548</v>
       </c>
       <c r="R2" t="n">
-        <v>6357402.56537766</v>
+        <v>6357470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Levide</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,19 +743,14 @@
           <t>2021-05-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lite</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,50 +781,58 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94011464</v>
+        <v>93025401</v>
       </c>
       <c r="B3" t="n">
-        <v>96361</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219864</v>
+        <v>102922</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Ängsnätfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Melitaea cinxia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ygne-Hemse, Gtl</t>
+          <t>Mallgårds ledningsgata, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698732.3484399756</v>
+        <v>698555</v>
       </c>
       <c r="R3" t="n">
-        <v>6357085.621724319</v>
+        <v>6357452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,32 +854,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Gerum</t>
+          <t>Levide</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Glest spridd</t>
+          <t>Större larver som lämnat spånaden.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,21 +878,1910 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>David Lundgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
+          <t>David Lundgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94011462</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99147</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>698573</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6357430</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94011464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99147</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>698733</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6357085</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Glest spridd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>94011465</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99147</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698681</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6357125</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94011490</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99147</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>698590</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6357359</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>94011767</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698593</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6357361</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94011769</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698723</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6357056</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>94011374</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698642</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6357246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94011825</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698727</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6357087</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fåtal</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94011828</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698724</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6357080</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>94011999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698554</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6357476</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Levide</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>94012001</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698559</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6357418</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>94012002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698711</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6357084</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94012003</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698722</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6357056</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>94011729</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>698583</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6357365</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Välspridd</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>94011931</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>698598</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6357403</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>94011932</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>698730</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6357088</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>94011936</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>698730</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6357060</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>94011651</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104641</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ygne-Hemse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>698725</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6357052</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gerum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-05-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 55649-2024 artfynd.xlsx
+++ b/artfynd/A 55649-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011832</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93025401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011462</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011465</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011490</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011767</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011769</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011374</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011825</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011828</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1958,6 +2018,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011999</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2064,6 +2129,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94012001</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94012002</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94012003</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2386,6 +2466,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011729</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011931</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2588,6 +2678,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011932</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2689,6 +2784,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011936</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,8 +2886,35 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94011651</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>